--- a/CRM_Model.xlsx
+++ b/CRM_Model.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Technology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BB4967-1282-45CD-9D88-EA32B528AFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E543E61A-B7A3-4BDD-AC0A-C3F92470EEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6839,14 +6839,14 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -15033,419 +15033,419 @@
       <c r="CZ8" s="51"/>
       <c r="DA8" s="51"/>
     </row>
-    <row r="9" spans="1:160" s="76" customFormat="1" ht="15">
-      <c r="B9" s="76" t="s">
+    <row r="9" spans="1:160" s="75" customFormat="1" ht="15">
+      <c r="B9" s="75" t="s">
         <v>141</v>
       </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
-      <c r="F9" s="79"/>
-      <c r="G9" s="79">
-        <f t="shared" ref="E9:BA9" si="9">G16/C16-1</f>
+      <c r="C9" s="76"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="78">
+        <f t="shared" ref="G9:BA9" si="9">G16/C16-1</f>
         <v>0.2358150213184651</v>
       </c>
-      <c r="H9" s="79">
+      <c r="H9" s="78">
         <f t="shared" si="9"/>
         <v>0.24770642201834847</v>
       </c>
-      <c r="I9" s="79">
+      <c r="I9" s="78">
         <f t="shared" si="9"/>
         <v>0.29833585476550684</v>
       </c>
-      <c r="J9" s="79">
+      <c r="J9" s="78">
         <f t="shared" si="9"/>
         <v>0.29067796610169494</v>
       </c>
-      <c r="K9" s="79">
+      <c r="K9" s="78">
         <f t="shared" si="9"/>
         <v>0.33864118895966011</v>
       </c>
-      <c r="L9" s="79">
+      <c r="L9" s="78">
         <f t="shared" si="9"/>
         <v>0.38438133874239355</v>
       </c>
-      <c r="M9" s="79">
+      <c r="M9" s="78">
         <f t="shared" si="9"/>
         <v>0.36168725238872046</v>
       </c>
-      <c r="N9" s="79">
+      <c r="N9" s="78">
         <f t="shared" si="9"/>
         <v>0.38301597723790759</v>
       </c>
-      <c r="O9" s="79">
+      <c r="O9" s="78">
         <f t="shared" si="9"/>
         <v>0.37886597938144329</v>
       </c>
-      <c r="P9" s="79">
+      <c r="P9" s="78">
         <f t="shared" si="9"/>
         <v>0.33992673992674005</v>
       </c>
-      <c r="Q9" s="79">
+      <c r="Q9" s="78">
         <f t="shared" si="9"/>
         <v>0.34930686291288726</v>
       </c>
-      <c r="R9" s="79">
+      <c r="R9" s="78">
         <f t="shared" si="9"/>
         <v>0.60800759613862954</v>
       </c>
-      <c r="S9" s="79">
+      <c r="S9" s="78">
         <f t="shared" si="9"/>
         <v>0.28339324227174689</v>
       </c>
-      <c r="T9" s="79">
+      <c r="T9" s="78">
         <f t="shared" si="9"/>
         <v>0.30822854018589396</v>
       </c>
-      <c r="U9" s="79">
+      <c r="U9" s="78">
         <f t="shared" si="9"/>
         <v>0.36478944698122784</v>
       </c>
-      <c r="V9" s="79">
+      <c r="V9" s="78">
         <f t="shared" si="9"/>
         <v>0.12705442377718734</v>
       </c>
-      <c r="W9" s="79">
+      <c r="W9" s="78">
         <f t="shared" si="9"/>
         <v>0.46336544924938394</v>
       </c>
-      <c r="X9" s="79">
+      <c r="X9" s="78">
         <f t="shared" si="9"/>
         <v>0.37770347926026515</v>
       </c>
-      <c r="Y9" s="79">
+      <c r="Y9" s="78">
         <f t="shared" si="9"/>
         <v>0.28596654275092948</v>
       </c>
-      <c r="Z9" s="79">
+      <c r="Z9" s="78">
         <f t="shared" si="9"/>
         <v>0.1920188613342646</v>
       </c>
-      <c r="AA9" s="79">
+      <c r="AA9" s="78">
         <f t="shared" si="9"/>
         <v>0.15694380646149142</v>
       </c>
-      <c r="AB9" s="79">
+      <c r="AB9" s="78">
         <f t="shared" si="9"/>
         <v>0.23972394964356147</v>
       </c>
-      <c r="AC9" s="79">
+      <c r="AC9" s="78">
         <f t="shared" si="9"/>
         <v>0.23726241237262413</v>
       </c>
-      <c r="AD9" s="79">
+      <c r="AD9" s="78">
         <f t="shared" si="9"/>
         <v>0.32547066149000092</v>
       </c>
-      <c r="AE9" s="79">
+      <c r="AE9" s="78">
         <f t="shared" si="9"/>
         <v>0.26826363155108512</v>
       </c>
-      <c r="AF9" s="79">
+      <c r="AF9" s="78">
         <f t="shared" si="9"/>
         <v>0.24585550865602235</v>
       </c>
-      <c r="AG9" s="79">
+      <c r="AG9" s="78">
         <f t="shared" si="9"/>
         <v>0.25280373831775704</v>
       </c>
-      <c r="AH9" s="79">
+      <c r="AH9" s="78">
         <f t="shared" si="9"/>
         <v>0.29269371062230576</v>
       </c>
-      <c r="AI9" s="79">
+      <c r="AI9" s="78">
         <f t="shared" si="9"/>
         <v>0.3487425649587812</v>
       </c>
-      <c r="AJ9" s="79">
+      <c r="AJ9" s="78">
         <f t="shared" si="9"/>
         <v>0.26534420111951307</v>
       </c>
-      <c r="AK9" s="79">
+      <c r="AK9" s="78">
         <f t="shared" si="9"/>
         <v>0.25932487877657584</v>
       </c>
-      <c r="AL9" s="79">
+      <c r="AL9" s="78">
         <f t="shared" si="9"/>
         <v>0.14450619923044039</v>
       </c>
-      <c r="AM9" s="79">
+      <c r="AM9" s="78">
         <f t="shared" si="9"/>
         <v>0.16286266924564807</v>
       </c>
-      <c r="AN9" s="79">
+      <c r="AN9" s="78">
         <f t="shared" si="9"/>
         <v>0.27318587504850611</v>
       </c>
-      <c r="AO9" s="79">
+      <c r="AO9" s="78">
         <f t="shared" si="9"/>
         <v>0.25583117363939278</v>
       </c>
-      <c r="AP9" s="79">
+      <c r="AP9" s="78">
         <f t="shared" si="9"/>
         <v>0.34590960029884199</v>
       </c>
-      <c r="AQ9" s="79">
+      <c r="AQ9" s="78">
         <f t="shared" si="9"/>
         <v>0.24318030605455765</v>
       </c>
-      <c r="AR9" s="79">
+      <c r="AR9" s="78">
         <f t="shared" si="9"/>
         <v>0.21822615056385253</v>
       </c>
-      <c r="AS9" s="79">
+      <c r="AS9" s="78">
         <f t="shared" si="9"/>
         <v>0.33048349056603765</v>
       </c>
-      <c r="AT9" s="79">
+      <c r="AT9" s="78">
         <f t="shared" si="9"/>
         <v>0.34637801831806825</v>
       </c>
-      <c r="AU9" s="79">
+      <c r="AU9" s="78">
         <f t="shared" si="9"/>
         <v>0.30184640085630177</v>
       </c>
-      <c r="AV9" s="79">
+      <c r="AV9" s="78">
         <f t="shared" si="9"/>
         <v>0.28871653740305225</v>
       </c>
-      <c r="AW9" s="79">
+      <c r="AW9" s="78">
         <f t="shared" si="9"/>
         <v>0.20075337912696645</v>
       </c>
-      <c r="AX9" s="79">
+      <c r="AX9" s="78">
         <f t="shared" si="9"/>
         <v>0.19913419913419905</v>
       </c>
-      <c r="AY9" s="79">
+      <c r="AY9" s="78">
         <f t="shared" si="9"/>
         <v>0.225693730729702</v>
       </c>
-      <c r="AZ9" s="79">
+      <c r="AZ9" s="78">
         <f t="shared" si="9"/>
         <v>0.23082896524946617</v>
       </c>
-      <c r="BA9" s="79">
+      <c r="BA9" s="78">
         <f t="shared" si="9"/>
         <v>0.26646982838162026</v>
       </c>
-      <c r="BB9" s="79">
+      <c r="BB9" s="78">
         <f>BB16/AX16-1</f>
         <v>0.25941206807632811</v>
       </c>
-      <c r="BC9" s="79">
+      <c r="BC9" s="78">
         <f t="shared" si="8"/>
         <v>0.24283078987087037</v>
       </c>
-      <c r="BD9" s="79">
+      <c r="BD9" s="78">
         <f t="shared" si="8"/>
         <v>0.21766561514195581</v>
       </c>
-      <c r="BE9" s="79">
+      <c r="BE9" s="78">
         <f t="shared" si="8"/>
         <v>0.14192044295497586</v>
       </c>
-      <c r="BF9" s="79">
+      <c r="BF9" s="78">
         <f t="shared" si="8"/>
         <v>0.14482664482664487</v>
       </c>
-      <c r="BG9" s="79">
+      <c r="BG9" s="78">
         <f t="shared" si="8"/>
         <v>0.11280528943462431</v>
       </c>
-      <c r="BH9" s="79">
+      <c r="BH9" s="78">
         <f t="shared" si="8"/>
         <v>0.11437823834196892</v>
       </c>
-      <c r="BI9" s="79">
+      <c r="BI9" s="78">
         <f t="shared" si="8"/>
         <v>0.11267066479520227</v>
       </c>
-      <c r="BJ9" s="79">
+      <c r="BJ9" s="78">
         <f t="shared" si="8"/>
         <v>0.10730893048765955</v>
       </c>
-      <c r="BK9" s="79">
+      <c r="BK9" s="78">
         <f t="shared" si="8"/>
         <v>0.10743300594155447</v>
       </c>
-      <c r="BL9" s="79">
+      <c r="BL9" s="78">
         <f t="shared" si="8"/>
         <v>8.3924212484017158E-2</v>
       </c>
-      <c r="BM9" s="79">
+      <c r="BM9" s="78">
         <f t="shared" si="8"/>
         <v>8.3027522935779752E-2</v>
       </c>
-      <c r="BN9" s="79">
+      <c r="BN9" s="78">
         <f t="shared" si="8"/>
         <v>7.6020243350920724E-2</v>
       </c>
-      <c r="BO9" s="79">
+      <c r="BO9" s="78">
         <f t="shared" si="8"/>
         <v>7.6207160845286337E-2</v>
       </c>
-      <c r="BP9" s="79">
+      <c r="BP9" s="78">
         <f t="shared" si="8"/>
         <v>9.7694369973190254E-2</v>
       </c>
-      <c r="BQ9" s="78"/>
-      <c r="BR9" s="78"/>
-      <c r="BS9" s="78"/>
-      <c r="BT9" s="78"/>
-      <c r="BU9" s="78"/>
-      <c r="BV9" s="78"/>
-      <c r="CA9" s="79"/>
-      <c r="CB9" s="79">
-        <f t="shared" ref="CA9:CL9" si="10">CB16/CA16-1</f>
+      <c r="BQ9" s="77"/>
+      <c r="BR9" s="77"/>
+      <c r="BS9" s="77"/>
+      <c r="BT9" s="77"/>
+      <c r="BU9" s="77"/>
+      <c r="BV9" s="77"/>
+      <c r="CA9" s="78"/>
+      <c r="CB9" s="78">
+        <f t="shared" ref="CB9:CL9" si="10">CB16/CA16-1</f>
         <v>0.26939869781692849</v>
       </c>
-      <c r="CC9" s="79">
+      <c r="CC9" s="78">
         <f t="shared" si="10"/>
         <v>0.36772869901037875</v>
       </c>
-      <c r="CD9" s="79">
+      <c r="CD9" s="78">
         <f t="shared" si="10"/>
         <v>0.42574781611223855</v>
       </c>
-      <c r="CE9" s="79">
+      <c r="CE9" s="78">
         <f t="shared" si="10"/>
         <v>0.25971654907785613</v>
       </c>
-      <c r="CF9" s="79">
+      <c r="CF9" s="78">
         <f t="shared" si="10"/>
         <v>0.32000294775111171</v>
       </c>
-      <c r="CG9" s="79">
+      <c r="CG9" s="78">
         <f t="shared" si="10"/>
         <v>0.24075107935090045</v>
       </c>
-      <c r="CH9" s="79">
+      <c r="CH9" s="78">
         <f t="shared" si="10"/>
         <v>0.265429784170504</v>
       </c>
-      <c r="CI9" s="79">
+      <c r="CI9" s="78">
         <f t="shared" si="10"/>
         <v>0.24925921536091034</v>
       </c>
-      <c r="CJ9" s="79">
+      <c r="CJ9" s="78">
         <f t="shared" si="10"/>
         <v>0.26015180265654658</v>
       </c>
-      <c r="CK9" s="79">
+      <c r="CK9" s="78">
         <f t="shared" si="10"/>
         <v>0.28730612859509108</v>
       </c>
-      <c r="CL9" s="79">
+      <c r="CL9" s="78">
         <f t="shared" si="10"/>
         <v>0.24295239209264241</v>
       </c>
-      <c r="CM9" s="79">
+      <c r="CM9" s="78">
         <f>CM16/CL16-1</f>
         <v>0.24656502917372491</v>
       </c>
-      <c r="CN9" s="79">
+      <c r="CN9" s="78">
         <f>AVERAGE(BC9:BF9)</f>
         <v>0.18681087319861173</v>
       </c>
-      <c r="CO9" s="79">
+      <c r="CO9" s="78">
         <f>AVERAGE(BG9:BJ9)</f>
         <v>0.11179078076486376</v>
       </c>
-      <c r="CP9" s="79">
+      <c r="CP9" s="78">
         <f>AVERAGE(BK9:BN9)</f>
         <v>8.7601246178068026E-2</v>
       </c>
-      <c r="CQ9" s="80">
+      <c r="CQ9" s="79">
         <f t="shared" ref="CQ9:CX9" si="11">CQ5/CP5-1</f>
         <v>8.6067489114659113E-2</v>
       </c>
-      <c r="CR9" s="80">
+      <c r="CR9" s="79">
         <f t="shared" si="11"/>
         <v>9.1019631849406979E-2</v>
       </c>
-      <c r="CS9" s="80">
+      <c r="CS9" s="79">
         <f t="shared" si="11"/>
         <v>0.12196317407220025</v>
       </c>
-      <c r="CT9" s="80">
+      <c r="CT9" s="79">
         <f t="shared" si="11"/>
         <v>0.10393236384880256</v>
       </c>
-      <c r="CU9" s="80">
+      <c r="CU9" s="79">
         <f t="shared" si="11"/>
         <v>8.54270085350195E-2</v>
       </c>
-      <c r="CV9" s="80">
+      <c r="CV9" s="79">
         <f t="shared" si="11"/>
         <v>6.6577682225841484E-2</v>
       </c>
-      <c r="CW9" s="80">
+      <c r="CW9" s="79">
         <f t="shared" si="11"/>
         <v>5.7199688210975763E-2</v>
       </c>
-      <c r="CX9" s="80">
+      <c r="CX9" s="79">
         <f t="shared" si="11"/>
         <v>4.7711435774435929E-2</v>
       </c>
-      <c r="CY9" s="78"/>
-      <c r="CZ9" s="78"/>
-      <c r="DA9" s="78"/>
-      <c r="DB9" s="78"/>
-      <c r="DC9" s="78"/>
-      <c r="DD9" s="78"/>
-      <c r="DE9" s="78"/>
-      <c r="DF9" s="78"/>
-      <c r="DG9" s="78"/>
-      <c r="DH9" s="78"/>
-      <c r="DI9" s="78"/>
-      <c r="DJ9" s="78"/>
-      <c r="DK9" s="78"/>
-      <c r="DL9" s="78"/>
-      <c r="DM9" s="78"/>
-      <c r="DN9" s="78"/>
-      <c r="DO9" s="78"/>
-      <c r="DP9" s="78"/>
-      <c r="DQ9" s="78"/>
-      <c r="DR9" s="78"/>
-      <c r="DS9" s="78"/>
-      <c r="DT9" s="78"/>
-      <c r="DU9" s="78"/>
-      <c r="DV9" s="78"/>
-      <c r="DW9" s="78"/>
-      <c r="DX9" s="78"/>
-      <c r="DY9" s="78"/>
-      <c r="DZ9" s="78"/>
-      <c r="EA9" s="78"/>
-      <c r="EB9" s="78"/>
-      <c r="EC9" s="78"/>
-      <c r="ED9" s="78"/>
-      <c r="EE9" s="78"/>
-      <c r="EF9" s="78"/>
-      <c r="EG9" s="78"/>
-      <c r="EH9" s="78"/>
-      <c r="EI9" s="78"/>
-      <c r="EJ9" s="78"/>
-      <c r="EK9" s="78"/>
-      <c r="EL9" s="78"/>
-      <c r="EM9" s="78"/>
-      <c r="EN9" s="78"/>
-      <c r="EO9" s="78"/>
-      <c r="EP9" s="78"/>
-      <c r="EQ9" s="78"/>
-      <c r="ER9" s="78"/>
-      <c r="ES9" s="78"/>
-      <c r="ET9" s="78"/>
-      <c r="EU9" s="78"/>
-      <c r="EV9" s="78"/>
-      <c r="EW9" s="78"/>
-      <c r="EX9" s="78"/>
-      <c r="EY9" s="78"/>
-      <c r="EZ9" s="78"/>
-      <c r="FA9" s="78"/>
-      <c r="FB9" s="78"/>
-      <c r="FC9" s="78"/>
-      <c r="FD9" s="78"/>
+      <c r="CY9" s="77"/>
+      <c r="CZ9" s="77"/>
+      <c r="DA9" s="77"/>
+      <c r="DB9" s="77"/>
+      <c r="DC9" s="77"/>
+      <c r="DD9" s="77"/>
+      <c r="DE9" s="77"/>
+      <c r="DF9" s="77"/>
+      <c r="DG9" s="77"/>
+      <c r="DH9" s="77"/>
+      <c r="DI9" s="77"/>
+      <c r="DJ9" s="77"/>
+      <c r="DK9" s="77"/>
+      <c r="DL9" s="77"/>
+      <c r="DM9" s="77"/>
+      <c r="DN9" s="77"/>
+      <c r="DO9" s="77"/>
+      <c r="DP9" s="77"/>
+      <c r="DQ9" s="77"/>
+      <c r="DR9" s="77"/>
+      <c r="DS9" s="77"/>
+      <c r="DT9" s="77"/>
+      <c r="DU9" s="77"/>
+      <c r="DV9" s="77"/>
+      <c r="DW9" s="77"/>
+      <c r="DX9" s="77"/>
+      <c r="DY9" s="77"/>
+      <c r="DZ9" s="77"/>
+      <c r="EA9" s="77"/>
+      <c r="EB9" s="77"/>
+      <c r="EC9" s="77"/>
+      <c r="ED9" s="77"/>
+      <c r="EE9" s="77"/>
+      <c r="EF9" s="77"/>
+      <c r="EG9" s="77"/>
+      <c r="EH9" s="77"/>
+      <c r="EI9" s="77"/>
+      <c r="EJ9" s="77"/>
+      <c r="EK9" s="77"/>
+      <c r="EL9" s="77"/>
+      <c r="EM9" s="77"/>
+      <c r="EN9" s="77"/>
+      <c r="EO9" s="77"/>
+      <c r="EP9" s="77"/>
+      <c r="EQ9" s="77"/>
+      <c r="ER9" s="77"/>
+      <c r="ES9" s="77"/>
+      <c r="ET9" s="77"/>
+      <c r="EU9" s="77"/>
+      <c r="EV9" s="77"/>
+      <c r="EW9" s="77"/>
+      <c r="EX9" s="77"/>
+      <c r="EY9" s="77"/>
+      <c r="EZ9" s="77"/>
+      <c r="FA9" s="77"/>
+      <c r="FB9" s="77"/>
+      <c r="FC9" s="77"/>
+      <c r="FD9" s="77"/>
     </row>
     <row r="10" spans="1:160" s="25" customFormat="1">
       <c r="C10" s="40"/>
@@ -27068,11 +27068,11 @@
         <f t="shared" ref="CP58:CP67" si="298">SUM(BK58:BN58)</f>
         <v>22729</v>
       </c>
-      <c r="CY58" s="75" t="str" cm="1">
+      <c r="CY58" s="80" t="str" cm="1">
         <f t="array" ref="CY58">_xlfn.IFS(CZ57&gt;=25%,"Strong Buy",CZ57&gt;=10.00001%,"Buy",AND(CZ57&lt;=10%,CZ57&gt;=-4.9999%),"Hold",AND(CZ57&lt;=-5%,CZ57&gt;=-14.999999%),"Sell",CZ57&lt;=-15%,"Strong Sell")</f>
         <v>Buy</v>
       </c>
-      <c r="CZ58" s="75"/>
+      <c r="CZ58" s="80"/>
     </row>
     <row r="59" spans="2:160">
       <c r="B59" s="1" t="s">

--- a/CRM_Model.xlsx
+++ b/CRM_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Technology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E543E61A-B7A3-4BDD-AC0A-C3F92470EEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8590BA-9D93-4553-A70B-A5AFB94D4499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="12435" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -6333,10 +6333,10 @@
     <t>https://www.gurufocus.com/term/wacc/CRM</t>
   </si>
   <si>
-    <t>9/3/2025</t>
-  </si>
-  <si>
     <t>Fiscal Year: [February - January]</t>
+  </si>
+  <si>
+    <t>1/10/2026</t>
   </si>
 </sst>
 </file>
@@ -13424,10 +13424,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="73">
-        <v>243.52</v>
+        <v>258.12</v>
       </c>
       <c r="D3" s="74" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="4" spans="2:19">
@@ -13438,7 +13438,7 @@
         <v>956</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="2:19">
@@ -13447,7 +13447,7 @@
       </c>
       <c r="C5" s="72">
         <f>C3*C4</f>
-        <v>232805.12</v>
+        <v>246762.72</v>
       </c>
     </row>
     <row r="6" spans="2:19">
@@ -13459,7 +13459,7 @@
         <v>15372</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="2:19">
@@ -13471,7 +13471,7 @@
         <v>8436</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="2:19">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C8" s="72">
         <f>C5-C6+C7</f>
-        <v>225869.12</v>
+        <v>239826.72</v>
       </c>
     </row>
     <row r="10" spans="2:19" ht="15">
@@ -13606,7 +13606,7 @@
     </row>
     <row r="20" spans="1:18">
       <c r="B20" s="1" t="s">
-        <v>2065</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="15">
@@ -26921,7 +26921,7 @@
       </c>
       <c r="CZ56" s="53">
         <f>Main!C3</f>
-        <v>243.52</v>
+        <v>258.12</v>
       </c>
       <c r="DA56" s="50"/>
       <c r="DB56" s="50"/>
@@ -26987,7 +26987,7 @@
       </c>
       <c r="CZ57" s="51">
         <f>CZ55/CZ56-1</f>
-        <v>0.23596458633606643</v>
+        <v>0.16605492044227055</v>
       </c>
       <c r="DA57" s="54" t="str">
         <f>IF(CZ57&gt;0,"Upside","Downside")</f>

--- a/CRM_Model.xlsx
+++ b/CRM_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Technology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8590BA-9D93-4553-A70B-A5AFB94D4499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D911291-7756-4580-ABB5-6F861231A640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="12435" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33390" yWindow="1470" windowWidth="21600" windowHeight="13185" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
